--- a/content_forms/009_media_content_distribution_assessment_form--content_forms.xlsx
+++ b/content_forms/009_media_content_distribution_assessment_form--content_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_cost</t>
+          <t>media_content_distribution_channels_cost_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Media Content Distribution Channels Cost</t>
+          <t>Media Content Distribution Channels Cost 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_impressions</t>
+          <t>media_content_distribution_channels_impressions_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Media Content Distribution Channels Impressions</t>
+          <t>Media Content Distribution Channels Impressions 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_reach</t>
+          <t>media_content_distribution_channels_reach_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Media Content Distribution Channels Reach</t>
+          <t>Media Content Distribution Channels Reach 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_frequency</t>
+          <t>media_content_distribution_channels_frequency_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Media Content Distribution Channels Frequency</t>
+          <t>Media Content Distribution Channels Frequency 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_engagement</t>
+          <t>media_content_distribution_channels_engagement_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Media Content Distribution Channels Engagement</t>
+          <t>Media Content Distribution Channels Engagement 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_cost</t>
+          <t>media_content_distribution_channels_cost_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Media Content Distribution Channels Cost</t>
+          <t>Media Content Distribution Channels Cost 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_impressions_choices</t>
+          <t>media_content_distribution_channels_impressions_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1540,7 +1540,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_impressions_choices</t>
+          <t>media_content_distribution_channels_impressions_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_impressions_choices</t>
+          <t>media_content_distribution_channels_impressions_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_impressions_choices</t>
+          <t>media_content_distribution_channels_impressions_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_impressions_choices</t>
+          <t>media_content_distribution_channels_impressions_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_reach_choices</t>
+          <t>media_content_distribution_channels_reach_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_reach_choices</t>
+          <t>media_content_distribution_channels_reach_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1642,7 +1642,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_reach_choices</t>
+          <t>media_content_distribution_channels_reach_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_reach_choices</t>
+          <t>media_content_distribution_channels_reach_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1676,7 +1676,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_frequency_choices</t>
+          <t>media_content_distribution_channels_frequency_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_frequency_choices</t>
+          <t>media_content_distribution_channels_frequency_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1710,7 +1710,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_frequency_choices</t>
+          <t>media_content_distribution_channels_frequency_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_frequency_choices</t>
+          <t>media_content_distribution_channels_frequency_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_frequency_choices</t>
+          <t>media_content_distribution_channels_frequency_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_engagement_choices</t>
+          <t>media_content_distribution_channels_engagement_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1778,7 +1778,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_engagement_choices</t>
+          <t>media_content_distribution_channels_engagement_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_engagement_choices</t>
+          <t>media_content_distribution_channels_engagement_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_engagement_choices</t>
+          <t>media_content_distribution_channels_engagement_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1829,7 +1829,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_cost_choices</t>
+          <t>media_content_distribution_channels_cost_3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_cost_choices</t>
+          <t>media_content_distribution_channels_cost_3_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_cost_choices</t>
+          <t>media_content_distribution_channels_cost_3_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1880,7 +1880,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_cost_choices</t>
+          <t>media_content_distribution_channels_cost_3_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>media_content_distribution_channels_cost_choices</t>
+          <t>media_content_distribution_channels_cost_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
